--- a/results/LCA/lci_comparison_ab/nickel_LCIA-results.xlsx
+++ b/results/LCA/lci_comparison_ab/nickel_LCIA-results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="40">
   <si>
     <t>index</t>
   </si>
@@ -43,67 +43,79 @@
     <t>IMPACT World+ Damage 2.1 for ecoinvent v3.10 | Human health | Total human health</t>
   </si>
   <si>
-    <t>Nickel equivalent | POX leaching of 19% Ni concentrate and refining to nickel metal | CA-NF | kilogram | Nickel</t>
-  </si>
-  <si>
-    <t>Nickel metal | Pyrometallurical sulfide ore | CA | kilogram | Nickel</t>
-  </si>
-  <si>
-    <t>nickel concentrate, 16% Ni | nickel mine operation and benefication to nickel concentrate, 16% Ni | CA-QC | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>nickel concentrate, 16% Ni | market for nickel concentrate, 16% Ni | World | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>nickel, class 1 | market for nickel, class 1 | World | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>nickel concentrate, 16% Ni | nickel mine operation and benefication to nickel concentrate, 16% Ni | CA | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>ni concentrate | [M+C] Nickel (Ni) ore mining and concentration (for Ni Class 1) | AU | kilogram | premise_generated_db_2025_L</t>
-  </si>
-  <si>
-    <t>nickel, class 1 | processing of nickel-rich materials | CA | kilogram | premise_generated_db_2025_L</t>
+    <t>nickel concentrate, 16% Ni | nickel mine operation and benefication to nickel concentrate, 16% Ni | CA-QC | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>nickel equivalent | POX leaching of 19% Ni concentrate and refining to nickel metal | CA-NF | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>nickel concentrate, 16% Ni | nickel mine operation and benefication to nickel concentrate, 16% Ni | CA | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>nickel, class 1 | processing of nickel-rich materials | CA | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>ni class 1 | [P+R] Nickel (Ni) class 1 production - Flash Smelting | AU | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>nickel concentrate, 16% Ni | market for nickel concentrate, 16% Ni | World | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>ni commodities | nickel (Ni) global market | GLO | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>nickel metal | pyrometallurical sulfide ore | CA | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>nickel, class 1 | market for nickel, class 1 | World | kilogram | premise_db_2025_L</t>
   </si>
   <si>
     <t>kilogram</t>
   </si>
   <si>
-    <t>Nickel equivalent</t>
-  </si>
-  <si>
-    <t>Nickel metal</t>
-  </si>
-  <si>
     <t>nickel concentrate, 16% Ni</t>
   </si>
   <si>
+    <t>nickel equivalent</t>
+  </si>
+  <si>
     <t>nickel, class 1</t>
   </si>
   <si>
-    <t>ni concentrate</t>
+    <t>ni class 1</t>
+  </si>
+  <si>
+    <t>ni commodities</t>
+  </si>
+  <si>
+    <t>nickel metal</t>
+  </si>
+  <si>
+    <t>nickel mine operation and benefication to nickel concentrate, 16% Ni</t>
   </si>
   <si>
     <t>POX leaching of 19% Ni concentrate and refining to nickel metal</t>
   </si>
   <si>
-    <t>Pyrometallurical sulfide ore</t>
-  </si>
-  <si>
-    <t>nickel mine operation and benefication to nickel concentrate, 16% Ni</t>
+    <t>processing of nickel-rich materials</t>
+  </si>
+  <si>
+    <t>[P+R] Nickel (Ni) class 1 production - Flash Smelting</t>
   </si>
   <si>
     <t>market for nickel concentrate, 16% Ni</t>
   </si>
   <si>
+    <t>nickel (Ni) global market</t>
+  </si>
+  <si>
+    <t>pyrometallurical sulfide ore</t>
+  </si>
+  <si>
     <t>market for nickel, class 1</t>
   </si>
   <si>
-    <t>[M+C] Nickel (Ni) ore mining and concentration (for Ni Class 1)</t>
-  </si>
-  <si>
-    <t>processing of nickel-rich materials</t>
+    <t>CA-QC</t>
   </si>
   <si>
     <t>CA-NF</t>
@@ -112,19 +124,16 @@
     <t>CA</t>
   </si>
   <si>
-    <t>CA-QC</t>
+    <t>AU</t>
   </si>
   <si>
     <t>World</t>
   </si>
   <si>
-    <t>AU</t>
-  </si>
-  <si>
-    <t>Nickel</t>
-  </si>
-  <si>
-    <t>premise_generated_db_2025_L</t>
+    <t>GLO</t>
+  </si>
+  <si>
+    <t>premise_db_2025_L</t>
   </si>
 </sst>
 </file>
@@ -482,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -525,25 +534,25 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I2">
-        <v>7.570756235522924</v>
+        <v>0.6001868101583324</v>
       </c>
       <c r="J2">
-        <v>8.088578869991704E-05</v>
+        <v>4.089705182901123E-06</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -557,25 +566,25 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I3">
-        <v>14.15658077738593</v>
+        <v>5.53167413554327</v>
       </c>
       <c r="J3">
-        <v>0.0001331714753054022</v>
+        <v>5.587172247674893E-05</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -589,25 +598,25 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4" t="s">
         <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I4">
-        <v>0.5931577870117358</v>
+        <v>0.5715067157033284</v>
       </c>
       <c r="J4">
-        <v>4.125400547588451E-06</v>
+        <v>3.797091636615174E-06</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -621,25 +630,25 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I5">
-        <v>0.7627906170535579</v>
+        <v>5.352119044656072</v>
       </c>
       <c r="J5">
-        <v>5.654033582234862E-06</v>
+        <v>4.077611861619732E-05</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -653,25 +662,25 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I6">
-        <v>46.05855505384164</v>
+        <v>10.66190101281931</v>
       </c>
       <c r="J6">
-        <v>0.0001196174556461331</v>
+        <v>9.820623421014017E-05</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -685,25 +694,25 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I7">
-        <v>0.5650434460063369</v>
+        <v>0.6981874258338735</v>
       </c>
       <c r="J7">
-        <v>3.824218165244819E-06</v>
+        <v>5.085680580426693E-06</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -717,25 +726,25 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I8">
-        <v>2.613557930373338</v>
+        <v>11.12584097732342</v>
       </c>
       <c r="J8">
-        <v>2.422888461841871E-05</v>
+        <v>1.235791280553221E-05</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -749,25 +758,57 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9">
+        <v>13.37317959813822</v>
+      </c>
+      <c r="J9">
+        <v>0.0001213794710266783</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="E9" t="s">
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
         <v>21</v>
       </c>
-      <c r="F9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9">
-        <v>5.336376646679591</v>
-      </c>
-      <c r="J9">
-        <v>4.185312837138313E-05</v>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10">
+        <v>45.75102460258649</v>
+      </c>
+      <c r="J10">
+        <v>0.0001153511941937934</v>
       </c>
     </row>
   </sheetData>

--- a/results/LCA/lci_comparison_ab/nickel_LCIA-results.xlsx
+++ b/results/LCA/lci_comparison_ab/nickel_LCIA-results.xlsx
@@ -1,20 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/fasc_metal_sustainability/results/LCA/lci_comparison_ab/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_355981EBF613C8264F2C4C75F5F301B17D924025" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F629702B-AC1F-4E16-B0C3-BBB993329F97}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$1</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="57">
   <si>
     <t>index</t>
   </si>
@@ -43,18 +52,30 @@
     <t>IMPACT World+ Damage 2.1 for ecoinvent v3.10 | Human health | Total human health</t>
   </si>
   <si>
+    <t>ni ore | [M] Nickel (Ni) ore mining (for NiSO4) | GLO | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
+    <t>niSO4 | ni ore mining and NiSO4 production worldwide | GLO | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
     <t>nickel concentrate, 16% Ni | nickel mine operation and benefication to nickel concentrate, 16% Ni | CA-QC | kilogram | premise_db_2025_L</t>
   </si>
   <si>
     <t>nickel equivalent | POX leaching of 19% Ni concentrate and refining to nickel metal | CA-NF | kilogram | premise_db_2025_L</t>
   </si>
   <si>
+    <t>ni matte | [P] Ni matte production (for NiSO4) | GLO | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
     <t>nickel concentrate, 16% Ni | nickel mine operation and benefication to nickel concentrate, 16% Ni | CA | kilogram | premise_db_2025_L</t>
   </si>
   <si>
     <t>nickel, class 1 | processing of nickel-rich materials | CA | kilogram | premise_db_2025_L</t>
   </si>
   <si>
+    <t>nickel sulfate | market for nickel sulfate | GLO | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
     <t>ni class 1 | [P+R] Nickel (Ni) class 1 production - Flash Smelting | AU | kilogram | premise_db_2025_L</t>
   </si>
   <si>
@@ -64,24 +85,42 @@
     <t>ni commodities | nickel (Ni) global market | GLO | kilogram | premise_db_2025_L</t>
   </si>
   <si>
+    <t>niSO4 | [P] Nickel sulfate (NiSO4) production | GLO | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
     <t>nickel metal | pyrometallurical sulfide ore | CA | kilogram | premise_db_2025_L</t>
   </si>
   <si>
     <t>nickel, class 1 | market for nickel, class 1 | World | kilogram | premise_db_2025_L</t>
   </si>
   <si>
+    <t>ni concentrate | [C] Ni ore concentration (for NiSO4) | GLO | kilogram | premise_db_2025_L</t>
+  </si>
+  <si>
     <t>kilogram</t>
   </si>
   <si>
+    <t>ni ore</t>
+  </si>
+  <si>
+    <t>niSO4</t>
+  </si>
+  <si>
     <t>nickel concentrate, 16% Ni</t>
   </si>
   <si>
     <t>nickel equivalent</t>
   </si>
   <si>
+    <t>ni matte</t>
+  </si>
+  <si>
     <t>nickel, class 1</t>
   </si>
   <si>
+    <t>nickel sulfate</t>
+  </si>
+  <si>
     <t>ni class 1</t>
   </si>
   <si>
@@ -91,15 +130,30 @@
     <t>nickel metal</t>
   </si>
   <si>
+    <t>ni concentrate</t>
+  </si>
+  <si>
+    <t>[M] Nickel (Ni) ore mining (for NiSO4)</t>
+  </si>
+  <si>
+    <t>ni ore mining and NiSO4 production worldwide</t>
+  </si>
+  <si>
     <t>nickel mine operation and benefication to nickel concentrate, 16% Ni</t>
   </si>
   <si>
     <t>POX leaching of 19% Ni concentrate and refining to nickel metal</t>
   </si>
   <si>
+    <t>[P] Ni matte production (for NiSO4)</t>
+  </si>
+  <si>
     <t>processing of nickel-rich materials</t>
   </si>
   <si>
+    <t>market for nickel sulfate</t>
+  </si>
+  <si>
     <t>[P+R] Nickel (Ni) class 1 production - Flash Smelting</t>
   </si>
   <si>
@@ -109,12 +163,21 @@
     <t>nickel (Ni) global market</t>
   </si>
   <si>
+    <t>[P] Nickel sulfate (NiSO4) production</t>
+  </si>
+  <si>
     <t>pyrometallurical sulfide ore</t>
   </si>
   <si>
     <t>market for nickel, class 1</t>
   </si>
   <si>
+    <t>[C] Ni ore concentration (for NiSO4)</t>
+  </si>
+  <si>
+    <t>GLO</t>
+  </si>
+  <si>
     <t>CA-QC</t>
   </si>
   <si>
@@ -128,9 +191,6 @@
   </si>
   <si>
     <t>World</t>
-  </si>
-  <si>
-    <t>GLO</t>
   </si>
   <si>
     <t>premise_db_2025_L</t>
@@ -139,8 +199,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,12 +217,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -192,24 +258,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -247,7 +322,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -281,6 +356,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -315,9 +391,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -490,11 +567,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="126.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="63.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -523,295 +612,492 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2">
+        <v>10.66190101281931</v>
+      </c>
+      <c r="J2">
+        <v>9.8206234210140175E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.57150671570332845</v>
+      </c>
+      <c r="J3" s="2">
+        <v>3.797091636615174E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4">
+        <v>5.3521190446560718</v>
+      </c>
+      <c r="J4">
+        <v>4.0776118616197319E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5">
+        <v>13.37317959813822</v>
+      </c>
+      <c r="J5">
+        <v>1.2137947102667831E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6">
+        <v>5.5316741355432697</v>
+      </c>
+      <c r="J6">
+        <v>5.5871722476748933E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7">
+        <v>0.60018681015833242</v>
+      </c>
+      <c r="J7">
+        <v>4.0897051829011231E-6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8">
+        <v>2.5248751473012549E-2</v>
+      </c>
+      <c r="J8">
+        <v>1.513105830609915E-7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" s="2">
+        <v>22.957175232175722</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1.149332639934173E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10">
+        <v>9.8759755565106637</v>
+      </c>
+      <c r="J10">
+        <v>4.6982975659679829E-5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="2">
+        <v>6.1988781087180742</v>
+      </c>
+      <c r="J11" s="2">
+        <v>7.6612654367005912E-5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12">
+        <v>11.125840977323421</v>
+      </c>
+      <c r="J12">
+        <v>1.2357912805532211E-5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13">
+        <v>1.5339866750808511</v>
+      </c>
+      <c r="J13">
+        <v>9.3815663459207124E-6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14">
+        <v>7.7949336715208845E-2</v>
+      </c>
+      <c r="J14">
+        <v>7.5692975762147682E-7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>9</v>
+      </c>
+      <c r="B15" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2">
-        <v>0.6001868101583324</v>
-      </c>
-      <c r="J2">
-        <v>4.089705182901123E-06</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3">
-        <v>5.53167413554327</v>
-      </c>
-      <c r="J3">
-        <v>5.587172247674893E-05</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4">
-        <v>0.5715067157033284</v>
-      </c>
-      <c r="J4">
-        <v>3.797091636615174E-06</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
         <v>27</v>
       </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5">
-        <v>5.352119044656072</v>
-      </c>
-      <c r="J5">
-        <v>4.077611861619732E-05</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="F15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0.6981874258338735</v>
+      </c>
+      <c r="J15" s="2">
+        <v>5.0856805804266934E-6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
         <v>13</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="B16" t="s">
         <v>22</v>
       </c>
-      <c r="F6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6">
-        <v>10.66190101281931</v>
-      </c>
-      <c r="J6">
-        <v>9.820623421014017E-05</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7">
-        <v>0.6981874258338735</v>
-      </c>
-      <c r="J7">
-        <v>5.085680580426693E-06</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
         <v>30</v>
       </c>
-      <c r="G8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8">
-        <v>11.12584097732342</v>
-      </c>
-      <c r="J8">
-        <v>1.235791280553221E-05</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" t="s">
-        <v>39</v>
-      </c>
-      <c r="I9">
-        <v>13.37317959813822</v>
-      </c>
-      <c r="J9">
-        <v>0.0001213794710266783</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" t="s">
-        <v>39</v>
-      </c>
-      <c r="I10">
+      <c r="F16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16">
         <v>45.75102460258649</v>
       </c>
-      <c r="J10">
-        <v>0.0001153511941937934</v>
+      <c r="J16">
+        <v>1.153511941937934E-4</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J16">
+      <sortCondition ref="G1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>